--- a/03_Continuous/04_Elastic_Net/c_data/elastic_net.xlsx
+++ b/03_Continuous/04_Elastic_Net/c_data/elastic_net.xlsx
@@ -1802,13 +1802,13 @@
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Processing/03_Blood_Correction/c_data/proteins_corrected.rds</t>
+    <t>01_Processing/03_Blood_Correction/c_data/blood_correction.rds</t>
   </si>
   <si>
     <t>35fac30909b3ec9c4ae9469c4edc26a0</t>
   </si>
   <si>
-    <t>01_Processing/06_Module_Building/c_data/modules.rds</t>
+    <t>01_Processing/06_Module_Building/c_data/module_building.rds</t>
   </si>
   <si>
     <t>32c36eae09056636394bdb0714dd608a</t>
@@ -1817,7 +1817,7 @@
     <t>singscore</t>
   </si>
   <si>
-    <t>01_Processing/05_Set_Scores/c_data/singscore.rds</t>
+    <t>01_Processing/05_Set_Scores/c_data/set_scores.rds</t>
   </si>
   <si>
     <t>aea708b70801bba711f0fc4e0138a11c</t>
